--- a/artfynd/A 51295-2024 artfynd.xlsx
+++ b/artfynd/A 51295-2024 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124616416</v>
+        <v>124616423</v>
       </c>
       <c r="B4" t="n">
-        <v>58055</v>
+        <v>58218</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,25 +915,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102990</v>
+        <v>103055</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124616423</v>
+        <v>124616416</v>
       </c>
       <c r="B5" t="n">
-        <v>58218</v>
+        <v>58055</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,25 +1029,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103055</v>
+        <v>102990</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">

--- a/artfynd/A 51295-2024 artfynd.xlsx
+++ b/artfynd/A 51295-2024 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124616423</v>
+        <v>124616416</v>
       </c>
       <c r="B4" t="n">
-        <v>58218</v>
+        <v>58055</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,25 +915,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103055</v>
+        <v>102990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124616416</v>
+        <v>124616423</v>
       </c>
       <c r="B5" t="n">
-        <v>58055</v>
+        <v>58218</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,25 +1029,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102990</v>
+        <v>103055</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">

--- a/artfynd/A 51295-2024 artfynd.xlsx
+++ b/artfynd/A 51295-2024 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124616423</v>
+        <v>124616416</v>
       </c>
       <c r="B4" t="n">
-        <v>58218</v>
+        <v>58167</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,25 +915,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103055</v>
+        <v>102990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124616416</v>
+        <v>124616423</v>
       </c>
       <c r="B5" t="n">
-        <v>58055</v>
+        <v>58345</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,25 +1029,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102990</v>
+        <v>103055</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
